--- a/WorkFlow Genie/backend/data/excel_files/326d7cf9-c754-42ec-8a13-06a5cf344bf5_students.xlsx
+++ b/WorkFlow Genie/backend/data/excel_files/326d7cf9-c754-42ec-8a13-06a5cf344bf5_students.xlsx
@@ -474,17 +474,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>maths</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Chem</t>
+          <t>english</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>science</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
